--- a/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语八年级上册.xlsx
+++ b/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语八年级上册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D233"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -999,6 +999,16 @@
           <t>in the countryside</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在乡村；在乡下；在农村</t>
@@ -1035,6 +1045,16 @@
           <t>die out</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 死绝
@@ -1048,6 +1068,16 @@
           <t>find out</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 查出；发现；看清…的面目；识破
@@ -1059,6 +1089,16 @@
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>go for a walk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1614,6 +1654,16 @@
           <t>a long time ago</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adv. 很久之前
@@ -1627,6 +1677,16 @@
           <t>challenge ... to ...</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 要求和(某人)(决斗；比赛)
@@ -1640,6 +1700,16 @@
           <t>and so on</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. “And so forth”的变体
@@ -1651,6 +1721,16 @@
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>copy down</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1759,6 +1839,16 @@
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>main unit</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2201,6 +2291,16 @@
           <t>work as</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 当；担任；担任…工作</t>
@@ -2213,6 +2313,16 @@
           <t>unaware of</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 不觉察
@@ -2226,6 +2336,16 @@
           <t>be unaware of</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 不知道；没有意识到；没意识到</t>
@@ -2238,6 +2358,16 @@
           <t>depend on</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 依靠
@@ -2251,6 +2381,16 @@
           <t>in addition</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 加之
@@ -2264,6 +2404,16 @@
           <t>grand total</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 总计；共计
@@ -2275,6 +2425,16 @@
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>look forward to</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -2585,6 +2745,16 @@
           <t>mobile phone</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 手机；移动电话
@@ -2853,6 +3023,16 @@
           <t>since then</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 以后；从此一直
@@ -2866,6 +3046,16 @@
           <t>keep in touch with</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 与…保持接触
@@ -2879,6 +3069,16 @@
           <t>in the daytime</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在白天
@@ -2892,6 +3092,16 @@
           <t>keep ... off</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 不让接近；不接近
@@ -2903,6 +3113,16 @@
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>at the same time</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -3222,6 +3442,16 @@
           <t>t'ai chi</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
           <t>太极拳，太极</t>
@@ -3347,6 +3577,16 @@
           <t>at first</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 首先
@@ -3360,6 +3600,16 @@
           <t>so far</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 就是那么些；到现在为止；到目前(此地)为止；就此范围来说
@@ -3373,6 +3623,16 @@
           <t>a bit of</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 一点儿
@@ -3386,6 +3646,16 @@
           <t>introduce ... to ...</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 介绍；介绍给；向……介绍</t>
@@ -3398,6 +3668,16 @@
           <t>come over</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 渡过来；(从敌方)过来；变挂；〔口语〕欺骗
@@ -3409,6 +3689,16 @@
       <c r="A141" s="2" t="inlineStr">
         <is>
           <t>come over to ...</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -4152,6 +4442,16 @@
           <t>act out</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 演出
@@ -4165,6 +4465,16 @@
           <t>make jokes about</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 拿……开玩笑；以某人为笑柄；讲笑话</t>
@@ -4177,6 +4487,16 @@
           <t>except for</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 只有
@@ -4190,6 +4510,16 @@
           <t>full of</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 总的说来；堆满；尽是；都
@@ -4203,6 +4533,16 @@
           <t>be full of</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 充满…(的)
@@ -4216,6 +4556,16 @@
           <t>in the end</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 终于
@@ -4227,6 +4577,16 @@
       <c r="A179" s="2" t="inlineStr">
         <is>
           <t>come on</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -4788,6 +5148,16 @@
           <t>take out</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 取出；带出(散步等)；除去(污点等)；取得(专卖权等)
@@ -4799,6 +5169,16 @@
       <c r="A204" s="2" t="inlineStr">
         <is>
           <t>pour out</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -5349,6 +5729,16 @@
           <t>treasure hunt</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 寻宝游戏（回答问题以获得匿藏的奖品）
@@ -5362,6 +5752,16 @@
           <t>in public</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 公然
@@ -5398,6 +5798,16 @@
           <t>in my opinion</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 我的意见是
@@ -5409,6 +5819,16 @@
       <c r="A232" s="2" t="inlineStr">
         <is>
           <t>above all</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
